--- a/experiments/psychopy/Visual_Imagery_DM_YZ/VI_practice_trig.xlsx
+++ b/experiments/psychopy/Visual_Imagery_DM_YZ/VI_practice_trig.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\borde\neurowaves-lab-documentation\experiments\psychopy\Visual_Imagery_DM_YZ\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hz3752\PycharmProjects\neurowaves-lab-documentation\experiments\psychopy\Visual_Imagery_DM_YZ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4225BE96-4DC9-4D11-A746-B6F03119BB3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FD85E71-CB48-4A94-8E18-E54796CDDBB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14010" yWindow="1340" windowWidth="8930" windowHeight="12340" xr2:uid="{775A8479-D045-4BFB-B0C0-DD78F6C659F0}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{775A8479-D045-4BFB-B0C0-DD78F6C659F0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,9 +27,10 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -44,9 +45,6 @@
     <t>BinaryCode</t>
   </si>
   <si>
-    <t>TrigNumber</t>
-  </si>
-  <si>
     <t>P_Sound start</t>
   </si>
   <si>
@@ -75,13 +73,16 @@
   </si>
   <si>
     <t>P_CQ_Key_Resp respond</t>
+  </si>
+  <si>
+    <t>Number of Triggers</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -448,13 +449,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6E741E8-D43F-474D-A93B-7701237DEC6C}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="35.54296875" customWidth="1"/>
-    <col min="2" max="2" width="39.26953125" customWidth="1"/>
+    <col min="1" max="1" width="35.5" customWidth="1"/>
+    <col min="2" max="2" width="39.25" customWidth="1"/>
+    <col min="3" max="3" width="18.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -462,59 +464,59 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>3</v>
-      </c>
       <c r="B2" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C2">
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C3">
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C4">
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C5">
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C6">
         <v>17</v>

--- a/experiments/psychopy/Visual_Imagery_DM_YZ/VI_practice_trig.xlsx
+++ b/experiments/psychopy/Visual_Imagery_DM_YZ/VI_practice_trig.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hz3752\PycharmProjects\neurowaves-lab-documentation\experiments\psychopy\Visual_Imagery_DM_YZ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FD85E71-CB48-4A94-8E18-E54796CDDBB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DF20E85-81CD-41EB-9159-B1D34803C8CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{775A8479-D045-4BFB-B0C0-DD78F6C659F0}"/>
   </bookViews>
